--- a/research/traditional_assets/database/data/norway/norway_computers_peripherals.xlsx
+++ b/research/traditional_assets/database/data/norway/norway_computers_peripherals.xlsx
@@ -587,23 +587,26 @@
           <t>Computers/Peripherals</t>
         </is>
       </c>
+      <c r="D2">
+        <v>0.148</v>
+      </c>
       <c r="G2">
-        <v>-0.005353602115003308</v>
+        <v>-0.06323051948051948</v>
       </c>
       <c r="H2">
-        <v>-0.01599471249173827</v>
+        <v>-0.1064935064935065</v>
       </c>
       <c r="I2">
-        <v>-0.1870456047587574</v>
+        <v>-0.2022727272727272</v>
       </c>
       <c r="J2">
-        <v>-0.1870456047587574</v>
+        <v>-0.2022727272727272</v>
       </c>
       <c r="K2">
-        <v>-53.26</v>
+        <v>-28.56</v>
       </c>
       <c r="L2">
-        <v>-0.3520158625247852</v>
+        <v>-0.2318181818181818</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -627,73 +630,67 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>19.88</v>
+        <v>7.380000000000001</v>
       </c>
       <c r="V2">
-        <v>0.08696412948381452</v>
+        <v>0.08934624697336563</v>
       </c>
       <c r="W2">
-        <v>0.4640825005540137</v>
+        <v>1.215631631631631</v>
       </c>
       <c r="X2">
-        <v>0.078820598191366</v>
+        <v>0.1457746728905048</v>
       </c>
       <c r="Y2">
-        <v>0.3852619023626477</v>
+        <v>1.069856958741127</v>
       </c>
       <c r="Z2">
-        <v>-13.14509122502172</v>
-      </c>
-      <c r="AA2">
-        <v>-0.1759226264713915</v>
+        <v>6.06299212598425</v>
       </c>
       <c r="AB2">
-        <v>0.06689429824494927</v>
-      </c>
-      <c r="AC2">
-        <v>-0.2428169247163407</v>
+        <v>0.1070996796101061</v>
       </c>
       <c r="AD2">
-        <v>53</v>
+        <v>49.4</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>53</v>
+        <v>49.4</v>
       </c>
       <c r="AG2">
-        <v>33.12</v>
+        <v>42.02</v>
       </c>
       <c r="AH2">
-        <v>0.1882102272727273</v>
+        <v>0.3742424242424242</v>
       </c>
       <c r="AI2">
-        <v>0.4744002864303616</v>
+        <v>0.6121437422552664</v>
       </c>
       <c r="AJ2">
-        <v>0.1265474552957359</v>
+        <v>0.337185042529289</v>
       </c>
       <c r="AK2">
-        <v>0.3606271777003485</v>
+        <v>0.5731042007637752</v>
       </c>
       <c r="AL2">
-        <v>17.92</v>
+        <v>4.383</v>
       </c>
       <c r="AM2">
-        <v>17.893</v>
+        <v>4.382</v>
       </c>
       <c r="AN2">
-        <v>-6.432038834951456</v>
+        <v>-4.843137254901961</v>
       </c>
       <c r="AO2">
-        <v>-1.579241071428572</v>
+        <v>-5.68560346794433</v>
       </c>
       <c r="AP2">
-        <v>-4.019417475728156</v>
+        <v>-4.119607843137254</v>
       </c>
       <c r="AQ2">
-        <v>-1.581624098809591</v>
+        <v>-5.686900958466453</v>
       </c>
     </row>
     <row r="3">
@@ -704,7 +701,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Ensurge Micropower ASA (OB:ENSU)</t>
+          <t>Techstep ASA (OB:TECH)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -712,8 +709,26 @@
           <t>Computers/Peripherals</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.148</v>
+      </c>
+      <c r="G3">
+        <v>0.05178571428571428</v>
+      </c>
+      <c r="H3">
+        <v>0.05178571428571428</v>
+      </c>
+      <c r="I3">
+        <v>-0.02857142857142857</v>
+      </c>
+      <c r="J3">
+        <v>-0.02857142857142857</v>
+      </c>
       <c r="K3">
-        <v>-43.5</v>
+        <v>-6.16</v>
+      </c>
+      <c r="L3">
+        <v>-0.05</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -737,73 +752,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>13.1</v>
+        <v>2.69</v>
       </c>
       <c r="V3">
-        <v>0.09244883556810163</v>
+        <v>0.07556179775280898</v>
       </c>
       <c r="W3">
-        <v>1.126943005181347</v>
+        <v>-0.09125925925925926</v>
       </c>
       <c r="X3">
-        <v>0.07457141770170567</v>
+        <v>0.1530218699891425</v>
       </c>
       <c r="Y3">
-        <v>1.052371587479642</v>
+        <v>-0.2442811292484018</v>
       </c>
       <c r="Z3">
-        <v>-0</v>
+        <v>6.06299212598425</v>
       </c>
       <c r="AA3">
-        <v>0.8922305764411027</v>
+        <v>-0.1732283464566929</v>
       </c>
       <c r="AB3">
-        <v>0.06785367044461162</v>
+        <v>0.1060294455976405</v>
       </c>
       <c r="AC3">
-        <v>0.824376905996491</v>
+        <v>-0.2792577920543333</v>
       </c>
       <c r="AD3">
-        <v>21.8</v>
+        <v>26.5</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>21.8</v>
+        <v>26.5</v>
       </c>
       <c r="AG3">
-        <v>8.700000000000001</v>
+        <v>23.81</v>
       </c>
       <c r="AH3">
-        <v>0.1333333333333333</v>
+        <v>0.426731078904992</v>
       </c>
       <c r="AI3">
-        <v>1.687306501547988</v>
+        <v>0.363013698630137</v>
       </c>
       <c r="AJ3">
-        <v>0.05784574468085108</v>
+        <v>0.400774280424171</v>
       </c>
       <c r="AK3">
-        <v>-48.33333333333341</v>
+        <v>0.3386431517565069</v>
       </c>
       <c r="AL3">
-        <v>16.9</v>
+        <v>0.993</v>
       </c>
       <c r="AM3">
-        <v>16.873</v>
+        <v>0.993</v>
       </c>
       <c r="AN3">
-        <v>-1.282352941176471</v>
+        <v>2.409090909090909</v>
       </c>
       <c r="AO3">
-        <v>-1.053254437869823</v>
+        <v>-3.544813695871098</v>
       </c>
       <c r="AP3">
-        <v>-0.511764705882353</v>
+        <v>2.164545454545455</v>
       </c>
       <c r="AQ3">
-        <v>-1.054939844722338</v>
+        <v>-3.544813695871098</v>
       </c>
     </row>
     <row r="4">
@@ -814,7 +829,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Techstep ASA (OB:TECH)</t>
+          <t>Ensurge Micropower ASA (OB:ENSU)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -822,23 +837,8 @@
           <t>Computers/Peripherals</t>
         </is>
       </c>
-      <c r="G4">
-        <v>0.06265697290152016</v>
-      </c>
-      <c r="H4">
-        <v>0.06265697290152016</v>
-      </c>
-      <c r="I4">
-        <v>-0.06939854593522801</v>
-      </c>
-      <c r="J4">
-        <v>-0.06939854593522801</v>
-      </c>
       <c r="K4">
-        <v>-9.76</v>
-      </c>
-      <c r="L4">
-        <v>-0.06450760079312623</v>
+        <v>-22.4</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -862,73 +862,64 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>6.78</v>
+        <v>4.69</v>
       </c>
       <c r="V4">
-        <v>0.07802071346375143</v>
+        <v>0.0997872340425532</v>
       </c>
       <c r="W4">
-        <v>-0.1987780040733197</v>
+        <v>2.522522522522522</v>
       </c>
       <c r="X4">
-        <v>0.08306977868102634</v>
+        <v>0.1385274757918672</v>
       </c>
       <c r="Y4">
-        <v>-0.2818477827543461</v>
-      </c>
-      <c r="Z4">
-        <v>17.92654028436018</v>
-      </c>
-      <c r="AA4">
-        <v>-1.244075829383886</v>
+        <v>2.383995046730655</v>
       </c>
       <c r="AB4">
-        <v>0.06593492604528692</v>
-      </c>
-      <c r="AC4">
-        <v>-1.310010755429172</v>
+        <v>0.1081699136225717</v>
       </c>
       <c r="AD4">
-        <v>31.2</v>
+        <v>22.9</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>31.2</v>
+        <v>22.9</v>
       </c>
       <c r="AG4">
-        <v>24.42</v>
+        <v>18.21</v>
       </c>
       <c r="AH4">
-        <v>0.2641828958509737</v>
+        <v>0.3276108726752503</v>
       </c>
       <c r="AI4">
-        <v>0.3157894736842105</v>
+        <v>2.974025974025974</v>
       </c>
       <c r="AJ4">
-        <v>0.2193675889328063</v>
+        <v>0.2792516485201656</v>
       </c>
       <c r="AK4">
-        <v>0.2653770919365355</v>
+        <v>6.049833887043192</v>
       </c>
       <c r="AL4">
-        <v>1.02</v>
+        <v>3.39</v>
       </c>
       <c r="AM4">
-        <v>1.02</v>
+        <v>3.389</v>
       </c>
       <c r="AN4">
-        <v>3.561643835616438</v>
+        <v>-1.080188679245283</v>
       </c>
       <c r="AO4">
-        <v>-10.29411764705882</v>
+        <v>-6.312684365781711</v>
       </c>
       <c r="AP4">
-        <v>2.787671232876712</v>
+        <v>-0.8589622641509433</v>
       </c>
       <c r="AQ4">
-        <v>-10.29411764705882</v>
+        <v>-6.314547064030687</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/norway/norway_computers_peripherals.xlsx
+++ b/research/traditional_assets/database/data/norway/norway_computers_peripherals.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.148</v>
+        <v>-0.2337</v>
       </c>
       <c r="G2">
-        <v>-0.06323051948051948</v>
+        <v>-0.08687154844724949</v>
       </c>
       <c r="H2">
-        <v>-0.1064935064935065</v>
+        <v>-0.1140357168471634</v>
       </c>
       <c r="I2">
-        <v>-0.2022727272727272</v>
+        <v>-0.1672882449974898</v>
       </c>
       <c r="J2">
-        <v>-0.2022727272727272</v>
+        <v>-0.1672882449974898</v>
       </c>
       <c r="K2">
-        <v>-28.56</v>
+        <v>-27.26</v>
       </c>
       <c r="L2">
-        <v>-0.2318181818181818</v>
+        <v>-0.2443878648784336</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,67 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>7.380000000000001</v>
+        <v>7.236000000000001</v>
       </c>
       <c r="V2">
-        <v>0.08934624697336563</v>
+        <v>0.1216134453781513</v>
       </c>
       <c r="W2">
-        <v>1.215631631631631</v>
+        <v>0.606018675721562</v>
       </c>
       <c r="X2">
-        <v>0.1457746728905048</v>
+        <v>0.1245632208035001</v>
       </c>
       <c r="Y2">
-        <v>1.069856958741127</v>
+        <v>0.4814554549180619</v>
       </c>
       <c r="Z2">
-        <v>6.06299212598425</v>
+        <v>5.803537981269511</v>
+      </c>
+      <c r="AA2">
+        <v>-1.752154721233637</v>
       </c>
       <c r="AB2">
-        <v>0.1070996796101061</v>
+        <v>0.09198454302163246</v>
+      </c>
+      <c r="AC2">
+        <v>-1.844139264255269</v>
       </c>
       <c r="AD2">
-        <v>49.4</v>
+        <v>37.59999999999999</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>49.4</v>
+        <v>37.59999999999999</v>
       </c>
       <c r="AG2">
-        <v>42.02</v>
+        <v>30.36399999999999</v>
       </c>
       <c r="AH2">
-        <v>0.3742424242424242</v>
+        <v>0.3872296601441812</v>
       </c>
       <c r="AI2">
-        <v>0.6121437422552664</v>
+        <v>0.4902216427640156</v>
       </c>
       <c r="AJ2">
-        <v>0.337185042529289</v>
+        <v>0.3378883646399002</v>
       </c>
       <c r="AK2">
-        <v>0.5731042007637752</v>
+        <v>0.4371185074283081</v>
       </c>
       <c r="AL2">
-        <v>4.383</v>
+        <v>7.19</v>
       </c>
       <c r="AM2">
-        <v>4.382</v>
+        <v>6.373</v>
       </c>
       <c r="AN2">
-        <v>-4.843137254901961</v>
+        <v>-11.75</v>
       </c>
       <c r="AO2">
-        <v>-5.68560346794433</v>
+        <v>-2.595271210013908</v>
       </c>
       <c r="AP2">
-        <v>-4.119607843137254</v>
+        <v>-9.48875</v>
       </c>
       <c r="AQ2">
-        <v>-5.686900958466453</v>
+        <v>-2.927977404675977</v>
       </c>
     </row>
     <row r="3">
@@ -710,25 +716,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.148</v>
+        <v>0.0296</v>
       </c>
       <c r="G3">
-        <v>0.05178571428571428</v>
+        <v>0.0652914798206278</v>
       </c>
       <c r="H3">
-        <v>0.05178571428571428</v>
+        <v>0.0652914798206278</v>
       </c>
       <c r="I3">
-        <v>-0.02857142857142857</v>
+        <v>-0.03282511210762332</v>
       </c>
       <c r="J3">
-        <v>-0.02857142857142857</v>
+        <v>-0.03282511210762332</v>
       </c>
       <c r="K3">
-        <v>-6.16</v>
+        <v>-6.66</v>
       </c>
       <c r="L3">
-        <v>-0.05</v>
+        <v>-0.05973094170403587</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -752,73 +758,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>2.69</v>
+        <v>6.36</v>
       </c>
       <c r="V3">
-        <v>0.07556179775280898</v>
+        <v>0.2271428571428571</v>
       </c>
       <c r="W3">
-        <v>-0.09125925925925926</v>
+        <v>-0.1432258064516129</v>
       </c>
       <c r="X3">
-        <v>0.1530218699891425</v>
+        <v>0.1268356730235164</v>
       </c>
       <c r="Y3">
-        <v>-0.2442811292484018</v>
+        <v>-0.2700614794751294</v>
       </c>
       <c r="Z3">
-        <v>6.06299212598425</v>
+        <v>7.631759069130733</v>
       </c>
       <c r="AA3">
-        <v>-0.1732283464566929</v>
+        <v>-0.2505133470225873</v>
       </c>
       <c r="AB3">
-        <v>0.1060294455976405</v>
+        <v>0.09137718908174705</v>
       </c>
       <c r="AC3">
-        <v>-0.2792577920543333</v>
+        <v>-0.3418905361043343</v>
       </c>
       <c r="AD3">
-        <v>26.5</v>
+        <v>19.2</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>26.5</v>
+        <v>19.2</v>
       </c>
       <c r="AG3">
-        <v>23.81</v>
+        <v>12.84</v>
       </c>
       <c r="AH3">
-        <v>0.426731078904992</v>
+        <v>0.4067796610169491</v>
       </c>
       <c r="AI3">
-        <v>0.363013698630137</v>
+        <v>0.2659279778393351</v>
       </c>
       <c r="AJ3">
-        <v>0.400774280424171</v>
+        <v>0.3143976493633692</v>
       </c>
       <c r="AK3">
-        <v>0.3386431517565069</v>
+        <v>0.1950182260024301</v>
       </c>
       <c r="AL3">
-        <v>0.993</v>
+        <v>2.54</v>
       </c>
       <c r="AM3">
-        <v>0.993</v>
+        <v>1.819</v>
       </c>
       <c r="AN3">
-        <v>2.409090909090909</v>
+        <v>1.699115044247787</v>
       </c>
       <c r="AO3">
-        <v>-3.544813695871098</v>
+        <v>-1.440944881889764</v>
       </c>
       <c r="AP3">
-        <v>2.164545454545455</v>
+        <v>1.136283185840708</v>
       </c>
       <c r="AQ3">
-        <v>-3.544813695871098</v>
+        <v>-2.012094557449148</v>
       </c>
     </row>
     <row r="4">
@@ -837,8 +843,26 @@
           <t>Computers/Peripherals</t>
         </is>
       </c>
+      <c r="D4">
+        <v>-0.4970000000000001</v>
+      </c>
+      <c r="G4">
+        <v>-385.6818181818182</v>
+      </c>
+      <c r="H4">
+        <v>-454.5454545454546</v>
+      </c>
+      <c r="I4">
+        <v>-340.9090909090909</v>
+      </c>
+      <c r="J4">
+        <v>-340.9090909090909</v>
+      </c>
       <c r="K4">
-        <v>-22.4</v>
+        <v>-20.6</v>
+      </c>
+      <c r="L4">
+        <v>-468.1818181818182</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -862,64 +886,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>4.69</v>
+        <v>0.876</v>
       </c>
       <c r="V4">
-        <v>0.0997872340425532</v>
+        <v>0.02780952380952381</v>
       </c>
       <c r="W4">
-        <v>2.522522522522522</v>
+        <v>1.355263157894737</v>
       </c>
       <c r="X4">
-        <v>0.1385274757918672</v>
+        <v>0.1222907685834838</v>
       </c>
       <c r="Y4">
-        <v>2.383995046730655</v>
+        <v>1.232972389311253</v>
+      </c>
+      <c r="Z4">
+        <v>0.009544468546637744</v>
+      </c>
+      <c r="AA4">
+        <v>-3.253796095444686</v>
       </c>
       <c r="AB4">
-        <v>0.1081699136225717</v>
+        <v>0.09259189696151787</v>
+      </c>
+      <c r="AC4">
+        <v>-3.346387992406204</v>
       </c>
       <c r="AD4">
-        <v>22.9</v>
+        <v>18.4</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>22.9</v>
+        <v>18.4</v>
       </c>
       <c r="AG4">
-        <v>18.21</v>
+        <v>17.524</v>
       </c>
       <c r="AH4">
-        <v>0.3276108726752503</v>
+        <v>0.3687374749498998</v>
       </c>
       <c r="AI4">
-        <v>2.974025974025974</v>
+        <v>4.08888888888889</v>
       </c>
       <c r="AJ4">
-        <v>0.2792516485201656</v>
+        <v>0.3574575718015665</v>
       </c>
       <c r="AK4">
-        <v>6.049833887043192</v>
+        <v>4.835540838852101</v>
       </c>
       <c r="AL4">
-        <v>3.39</v>
+        <v>4.65</v>
       </c>
       <c r="AM4">
-        <v>3.389</v>
+        <v>4.554</v>
       </c>
       <c r="AN4">
-        <v>-1.080188679245283</v>
+        <v>-1.268965517241379</v>
       </c>
       <c r="AO4">
-        <v>-6.312684365781711</v>
+        <v>-3.225806451612903</v>
       </c>
       <c r="AP4">
-        <v>-0.8589622641509433</v>
+        <v>-1.208551724137931</v>
       </c>
       <c r="AQ4">
-        <v>-6.314547064030687</v>
+        <v>-3.293807641633729</v>
       </c>
     </row>
   </sheetData>
